--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863208</v>
+        <v>124863049</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451244</v>
+        <v>451155</v>
       </c>
       <c r="R2" t="n">
-        <v>6709610</v>
+        <v>6709561</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863157</v>
+        <v>124863263</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451181</v>
+        <v>451367</v>
       </c>
       <c r="R3" t="n">
-        <v>6709688</v>
+        <v>6709547</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863193</v>
+        <v>124863258</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451220</v>
+        <v>451347</v>
       </c>
       <c r="R4" t="n">
-        <v>6709614</v>
+        <v>6709539</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124862972</v>
+        <v>124863201</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451167</v>
+        <v>451250</v>
       </c>
       <c r="R5" t="n">
-        <v>6709559</v>
+        <v>6709591</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863049</v>
+        <v>124862912</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451155</v>
+        <v>451208</v>
       </c>
       <c r="R6" t="n">
-        <v>6709561</v>
+        <v>6709512</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863201</v>
+        <v>124863141</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451250</v>
+        <v>451172</v>
       </c>
       <c r="R7" t="n">
-        <v>6709591</v>
+        <v>6709678</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863258</v>
+        <v>124862901</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451347</v>
+        <v>451194</v>
       </c>
       <c r="R8" t="n">
-        <v>6709539</v>
+        <v>6709513</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124862987</v>
+        <v>124863193</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451183</v>
+        <v>451220</v>
       </c>
       <c r="R9" t="n">
-        <v>6709547</v>
+        <v>6709614</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124862955</v>
+        <v>124863180</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451085</v>
+        <v>451234</v>
       </c>
       <c r="R10" t="n">
-        <v>6709545</v>
+        <v>6709587</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124862912</v>
+        <v>124863208</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451208</v>
+        <v>451244</v>
       </c>
       <c r="R11" t="n">
-        <v>6709512</v>
+        <v>6709610</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863186</v>
+        <v>124863021</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451213</v>
+        <v>451148</v>
       </c>
       <c r="R12" t="n">
-        <v>6709596</v>
+        <v>6709550</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863010</v>
+        <v>124862987</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451163</v>
+        <v>451183</v>
       </c>
       <c r="R13" t="n">
-        <v>6709539</v>
+        <v>6709547</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863173</v>
+        <v>124863157</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451230</v>
+        <v>451181</v>
       </c>
       <c r="R14" t="n">
-        <v>6709603</v>
+        <v>6709688</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124862901</v>
+        <v>124863186</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451194</v>
+        <v>451213</v>
       </c>
       <c r="R15" t="n">
-        <v>6709513</v>
+        <v>6709596</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863180</v>
+        <v>124862955</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451234</v>
+        <v>451085</v>
       </c>
       <c r="R16" t="n">
-        <v>6709587</v>
+        <v>6709545</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863263</v>
+        <v>124863173</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451367</v>
+        <v>451230</v>
       </c>
       <c r="R17" t="n">
-        <v>6709547</v>
+        <v>6709603</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863021</v>
+        <v>124862972</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451148</v>
+        <v>451167</v>
       </c>
       <c r="R18" t="n">
-        <v>6709550</v>
+        <v>6709559</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863141</v>
+        <v>124863010</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451172</v>
+        <v>451163</v>
       </c>
       <c r="R19" t="n">
-        <v>6709678</v>
+        <v>6709539</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863049</v>
+        <v>124863193</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451155</v>
+        <v>451220</v>
       </c>
       <c r="R2" t="n">
-        <v>6709561</v>
+        <v>6709614</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863258</v>
+        <v>124862912</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451347</v>
+        <v>451208</v>
       </c>
       <c r="R4" t="n">
-        <v>6709539</v>
+        <v>6709512</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863201</v>
+        <v>124863208</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451250</v>
+        <v>451244</v>
       </c>
       <c r="R5" t="n">
-        <v>6709591</v>
+        <v>6709610</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124862912</v>
+        <v>124863021</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451208</v>
+        <v>451148</v>
       </c>
       <c r="R6" t="n">
-        <v>6709512</v>
+        <v>6709550</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863141</v>
+        <v>124863180</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451172</v>
+        <v>451234</v>
       </c>
       <c r="R7" t="n">
-        <v>6709678</v>
+        <v>6709587</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124862901</v>
+        <v>124863010</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451194</v>
+        <v>451163</v>
       </c>
       <c r="R8" t="n">
-        <v>6709513</v>
+        <v>6709539</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863193</v>
+        <v>124862972</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451220</v>
+        <v>451167</v>
       </c>
       <c r="R9" t="n">
-        <v>6709614</v>
+        <v>6709559</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863180</v>
+        <v>124863173</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451234</v>
+        <v>451230</v>
       </c>
       <c r="R10" t="n">
-        <v>6709587</v>
+        <v>6709603</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863208</v>
+        <v>124863049</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451244</v>
+        <v>451155</v>
       </c>
       <c r="R11" t="n">
-        <v>6709610</v>
+        <v>6709561</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863021</v>
+        <v>124863201</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451148</v>
+        <v>451250</v>
       </c>
       <c r="R12" t="n">
-        <v>6709550</v>
+        <v>6709591</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124862987</v>
+        <v>124863186</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451183</v>
+        <v>451213</v>
       </c>
       <c r="R13" t="n">
-        <v>6709547</v>
+        <v>6709596</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863157</v>
+        <v>124863141</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451181</v>
+        <v>451172</v>
       </c>
       <c r="R14" t="n">
-        <v>6709688</v>
+        <v>6709678</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863186</v>
+        <v>124862901</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451213</v>
+        <v>451194</v>
       </c>
       <c r="R15" t="n">
-        <v>6709596</v>
+        <v>6709513</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124862955</v>
+        <v>124863157</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451085</v>
+        <v>451181</v>
       </c>
       <c r="R16" t="n">
-        <v>6709545</v>
+        <v>6709688</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863173</v>
+        <v>124863258</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451230</v>
+        <v>451347</v>
       </c>
       <c r="R17" t="n">
-        <v>6709603</v>
+        <v>6709539</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124862972</v>
+        <v>124862987</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451167</v>
+        <v>451183</v>
       </c>
       <c r="R18" t="n">
-        <v>6709559</v>
+        <v>6709547</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863010</v>
+        <v>124862955</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451163</v>
+        <v>451085</v>
       </c>
       <c r="R19" t="n">
-        <v>6709539</v>
+        <v>6709545</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863193</v>
+        <v>124863258</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451220</v>
+        <v>451347</v>
       </c>
       <c r="R2" t="n">
-        <v>6709614</v>
+        <v>6709539</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863263</v>
+        <v>124862912</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451367</v>
+        <v>451208</v>
       </c>
       <c r="R3" t="n">
-        <v>6709547</v>
+        <v>6709512</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124862912</v>
+        <v>124863208</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451208</v>
+        <v>451244</v>
       </c>
       <c r="R4" t="n">
-        <v>6709512</v>
+        <v>6709610</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863208</v>
+        <v>124863193</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451244</v>
+        <v>451220</v>
       </c>
       <c r="R5" t="n">
-        <v>6709610</v>
+        <v>6709614</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863180</v>
+        <v>124862955</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451234</v>
+        <v>451085</v>
       </c>
       <c r="R7" t="n">
-        <v>6709587</v>
+        <v>6709545</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863010</v>
+        <v>124863263</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451163</v>
+        <v>451367</v>
       </c>
       <c r="R8" t="n">
-        <v>6709539</v>
+        <v>6709547</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124862972</v>
+        <v>124863141</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451167</v>
+        <v>451172</v>
       </c>
       <c r="R9" t="n">
-        <v>6709559</v>
+        <v>6709678</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863173</v>
+        <v>124863201</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451230</v>
+        <v>451250</v>
       </c>
       <c r="R10" t="n">
-        <v>6709603</v>
+        <v>6709591</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863049</v>
+        <v>124863180</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451155</v>
+        <v>451234</v>
       </c>
       <c r="R11" t="n">
-        <v>6709561</v>
+        <v>6709587</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863201</v>
+        <v>124862987</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451250</v>
+        <v>451183</v>
       </c>
       <c r="R12" t="n">
-        <v>6709591</v>
+        <v>6709547</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863186</v>
+        <v>124862972</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451213</v>
+        <v>451167</v>
       </c>
       <c r="R13" t="n">
-        <v>6709596</v>
+        <v>6709559</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863141</v>
+        <v>124863186</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451172</v>
+        <v>451213</v>
       </c>
       <c r="R14" t="n">
-        <v>6709678</v>
+        <v>6709596</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124862901</v>
+        <v>124863157</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451194</v>
+        <v>451181</v>
       </c>
       <c r="R15" t="n">
-        <v>6709513</v>
+        <v>6709688</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863157</v>
+        <v>124863049</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451181</v>
+        <v>451155</v>
       </c>
       <c r="R16" t="n">
-        <v>6709688</v>
+        <v>6709561</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863258</v>
+        <v>124863010</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451347</v>
+        <v>451163</v>
       </c>
       <c r="R17" t="n">
         <v>6709539</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124862987</v>
+        <v>124863173</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451183</v>
+        <v>451230</v>
       </c>
       <c r="R18" t="n">
-        <v>6709547</v>
+        <v>6709603</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124862955</v>
+        <v>124862901</v>
       </c>
       <c r="B19" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451085</v>
+        <v>451194</v>
       </c>
       <c r="R19" t="n">
-        <v>6709545</v>
+        <v>6709513</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863258</v>
+        <v>124863193</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451347</v>
+        <v>451220</v>
       </c>
       <c r="R2" t="n">
-        <v>6709539</v>
+        <v>6709614</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124862912</v>
+        <v>124863201</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451208</v>
+        <v>451250</v>
       </c>
       <c r="R3" t="n">
-        <v>6709512</v>
+        <v>6709591</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863208</v>
+        <v>124863049</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451244</v>
+        <v>451155</v>
       </c>
       <c r="R4" t="n">
-        <v>6709610</v>
+        <v>6709561</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863193</v>
+        <v>124863258</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451220</v>
+        <v>451347</v>
       </c>
       <c r="R5" t="n">
-        <v>6709614</v>
+        <v>6709539</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863021</v>
+        <v>124862987</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451148</v>
+        <v>451183</v>
       </c>
       <c r="R6" t="n">
-        <v>6709550</v>
+        <v>6709547</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124862955</v>
+        <v>124863141</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451085</v>
+        <v>451172</v>
       </c>
       <c r="R7" t="n">
-        <v>6709545</v>
+        <v>6709678</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863263</v>
+        <v>124862955</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451367</v>
+        <v>451085</v>
       </c>
       <c r="R8" t="n">
-        <v>6709547</v>
+        <v>6709545</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863141</v>
+        <v>124863263</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451172</v>
+        <v>451367</v>
       </c>
       <c r="R9" t="n">
-        <v>6709678</v>
+        <v>6709547</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863201</v>
+        <v>124862901</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451250</v>
+        <v>451194</v>
       </c>
       <c r="R10" t="n">
-        <v>6709591</v>
+        <v>6709513</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863180</v>
+        <v>124863173</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451234</v>
+        <v>451230</v>
       </c>
       <c r="R11" t="n">
-        <v>6709587</v>
+        <v>6709603</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124862987</v>
+        <v>124863021</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451183</v>
+        <v>451148</v>
       </c>
       <c r="R12" t="n">
-        <v>6709547</v>
+        <v>6709550</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124862972</v>
+        <v>124863180</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451167</v>
+        <v>451234</v>
       </c>
       <c r="R13" t="n">
-        <v>6709559</v>
+        <v>6709587</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863186</v>
+        <v>124863208</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451213</v>
+        <v>451244</v>
       </c>
       <c r="R14" t="n">
-        <v>6709596</v>
+        <v>6709610</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863049</v>
+        <v>124862912</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451155</v>
+        <v>451208</v>
       </c>
       <c r="R16" t="n">
-        <v>6709561</v>
+        <v>6709512</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863010</v>
+        <v>124863186</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451163</v>
+        <v>451213</v>
       </c>
       <c r="R17" t="n">
-        <v>6709539</v>
+        <v>6709596</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863173</v>
+        <v>124862972</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451230</v>
+        <v>451167</v>
       </c>
       <c r="R18" t="n">
-        <v>6709603</v>
+        <v>6709559</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124862901</v>
+        <v>124863010</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451194</v>
+        <v>451163</v>
       </c>
       <c r="R19" t="n">
-        <v>6709513</v>
+        <v>6709539</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863193</v>
+        <v>124863258</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451220</v>
+        <v>451347</v>
       </c>
       <c r="R2" t="n">
-        <v>6709614</v>
+        <v>6709539</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863201</v>
+        <v>124863049</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451250</v>
+        <v>451155</v>
       </c>
       <c r="R3" t="n">
-        <v>6709591</v>
+        <v>6709561</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863049</v>
+        <v>124863263</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451155</v>
+        <v>451367</v>
       </c>
       <c r="R4" t="n">
-        <v>6709561</v>
+        <v>6709547</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863258</v>
+        <v>124863201</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451347</v>
+        <v>451250</v>
       </c>
       <c r="R5" t="n">
-        <v>6709539</v>
+        <v>6709591</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124862987</v>
+        <v>124863021</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451183</v>
+        <v>451148</v>
       </c>
       <c r="R6" t="n">
-        <v>6709547</v>
+        <v>6709550</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863141</v>
+        <v>124863193</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451172</v>
+        <v>451220</v>
       </c>
       <c r="R7" t="n">
-        <v>6709678</v>
+        <v>6709614</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124862955</v>
+        <v>124863141</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451085</v>
+        <v>451172</v>
       </c>
       <c r="R8" t="n">
-        <v>6709545</v>
+        <v>6709678</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863263</v>
+        <v>124863157</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451367</v>
+        <v>451181</v>
       </c>
       <c r="R9" t="n">
-        <v>6709547</v>
+        <v>6709688</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124862901</v>
+        <v>124863010</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451194</v>
+        <v>451163</v>
       </c>
       <c r="R10" t="n">
-        <v>6709513</v>
+        <v>6709539</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863173</v>
+        <v>124862912</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451230</v>
+        <v>451208</v>
       </c>
       <c r="R11" t="n">
-        <v>6709603</v>
+        <v>6709512</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863021</v>
+        <v>124862955</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451148</v>
+        <v>451085</v>
       </c>
       <c r="R12" t="n">
-        <v>6709550</v>
+        <v>6709545</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863180</v>
+        <v>124863186</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451234</v>
+        <v>451213</v>
       </c>
       <c r="R13" t="n">
-        <v>6709587</v>
+        <v>6709596</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863208</v>
+        <v>124862972</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451244</v>
+        <v>451167</v>
       </c>
       <c r="R14" t="n">
-        <v>6709610</v>
+        <v>6709559</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863157</v>
+        <v>124862987</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451181</v>
+        <v>451183</v>
       </c>
       <c r="R15" t="n">
-        <v>6709688</v>
+        <v>6709547</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124862912</v>
+        <v>124863180</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451208</v>
+        <v>451234</v>
       </c>
       <c r="R16" t="n">
-        <v>6709512</v>
+        <v>6709587</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863186</v>
+        <v>124862901</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451213</v>
+        <v>451194</v>
       </c>
       <c r="R17" t="n">
-        <v>6709596</v>
+        <v>6709513</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124862972</v>
+        <v>124863208</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451167</v>
+        <v>451244</v>
       </c>
       <c r="R18" t="n">
-        <v>6709559</v>
+        <v>6709610</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863010</v>
+        <v>124863173</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451163</v>
+        <v>451230</v>
       </c>
       <c r="R19" t="n">
-        <v>6709539</v>
+        <v>6709603</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863258</v>
+        <v>124862912</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451347</v>
+        <v>451208</v>
       </c>
       <c r="R2" t="n">
-        <v>6709539</v>
+        <v>6709512</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863049</v>
+        <v>124863010</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451155</v>
+        <v>451163</v>
       </c>
       <c r="R3" t="n">
-        <v>6709561</v>
+        <v>6709539</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863263</v>
+        <v>124863141</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451367</v>
+        <v>451172</v>
       </c>
       <c r="R4" t="n">
-        <v>6709547</v>
+        <v>6709678</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863201</v>
+        <v>124863186</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451250</v>
+        <v>451213</v>
       </c>
       <c r="R5" t="n">
-        <v>6709591</v>
+        <v>6709596</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863021</v>
+        <v>124863258</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451148</v>
+        <v>451347</v>
       </c>
       <c r="R6" t="n">
-        <v>6709550</v>
+        <v>6709539</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863193</v>
+        <v>124863263</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451220</v>
+        <v>451367</v>
       </c>
       <c r="R7" t="n">
-        <v>6709614</v>
+        <v>6709547</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863141</v>
+        <v>124863180</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451172</v>
+        <v>451234</v>
       </c>
       <c r="R8" t="n">
-        <v>6709678</v>
+        <v>6709587</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863157</v>
+        <v>124862987</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451181</v>
+        <v>451183</v>
       </c>
       <c r="R9" t="n">
-        <v>6709688</v>
+        <v>6709547</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863010</v>
+        <v>124863208</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451163</v>
+        <v>451244</v>
       </c>
       <c r="R10" t="n">
-        <v>6709539</v>
+        <v>6709610</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124862912</v>
+        <v>124863157</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451208</v>
+        <v>451181</v>
       </c>
       <c r="R11" t="n">
-        <v>6709512</v>
+        <v>6709688</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124862955</v>
+        <v>124863201</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451085</v>
+        <v>451250</v>
       </c>
       <c r="R12" t="n">
-        <v>6709545</v>
+        <v>6709591</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863186</v>
+        <v>124862955</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451213</v>
+        <v>451085</v>
       </c>
       <c r="R13" t="n">
-        <v>6709596</v>
+        <v>6709545</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124862987</v>
+        <v>124863021</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451183</v>
+        <v>451148</v>
       </c>
       <c r="R15" t="n">
-        <v>6709547</v>
+        <v>6709550</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863180</v>
+        <v>124863193</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451234</v>
+        <v>451220</v>
       </c>
       <c r="R16" t="n">
-        <v>6709587</v>
+        <v>6709614</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124862901</v>
+        <v>124863049</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451194</v>
+        <v>451155</v>
       </c>
       <c r="R17" t="n">
-        <v>6709513</v>
+        <v>6709561</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863208</v>
+        <v>124862901</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451244</v>
+        <v>451194</v>
       </c>
       <c r="R18" t="n">
-        <v>6709610</v>
+        <v>6709513</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124862912</v>
+        <v>124863180</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451208</v>
+        <v>451234</v>
       </c>
       <c r="R2" t="n">
-        <v>6709512</v>
+        <v>6709587</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863010</v>
+        <v>124863193</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451163</v>
+        <v>451220</v>
       </c>
       <c r="R3" t="n">
-        <v>6709539</v>
+        <v>6709614</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863141</v>
+        <v>124863010</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451172</v>
+        <v>451163</v>
       </c>
       <c r="R4" t="n">
-        <v>6709678</v>
+        <v>6709539</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863186</v>
+        <v>124862955</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451213</v>
+        <v>451085</v>
       </c>
       <c r="R5" t="n">
-        <v>6709596</v>
+        <v>6709545</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863258</v>
+        <v>124863049</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451347</v>
+        <v>451155</v>
       </c>
       <c r="R6" t="n">
-        <v>6709539</v>
+        <v>6709561</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863263</v>
+        <v>124863201</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451367</v>
+        <v>451250</v>
       </c>
       <c r="R7" t="n">
-        <v>6709547</v>
+        <v>6709591</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863180</v>
+        <v>124863021</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451234</v>
+        <v>451148</v>
       </c>
       <c r="R8" t="n">
-        <v>6709587</v>
+        <v>6709550</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124862987</v>
+        <v>124862912</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451183</v>
+        <v>451208</v>
       </c>
       <c r="R9" t="n">
-        <v>6709547</v>
+        <v>6709512</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863208</v>
+        <v>124862987</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451244</v>
+        <v>451183</v>
       </c>
       <c r="R10" t="n">
-        <v>6709610</v>
+        <v>6709547</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863157</v>
+        <v>124863173</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451181</v>
+        <v>451230</v>
       </c>
       <c r="R11" t="n">
-        <v>6709688</v>
+        <v>6709603</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863201</v>
+        <v>124862972</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451250</v>
+        <v>451167</v>
       </c>
       <c r="R12" t="n">
-        <v>6709591</v>
+        <v>6709559</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124862955</v>
+        <v>124862901</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451085</v>
+        <v>451194</v>
       </c>
       <c r="R13" t="n">
-        <v>6709545</v>
+        <v>6709513</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124862972</v>
+        <v>124863141</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451167</v>
+        <v>451172</v>
       </c>
       <c r="R14" t="n">
-        <v>6709559</v>
+        <v>6709678</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863021</v>
+        <v>124863186</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451148</v>
+        <v>451213</v>
       </c>
       <c r="R15" t="n">
-        <v>6709550</v>
+        <v>6709596</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863193</v>
+        <v>124863157</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451220</v>
+        <v>451181</v>
       </c>
       <c r="R16" t="n">
-        <v>6709614</v>
+        <v>6709688</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863049</v>
+        <v>124863208</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451155</v>
+        <v>451244</v>
       </c>
       <c r="R17" t="n">
-        <v>6709561</v>
+        <v>6709610</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124862901</v>
+        <v>124863258</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451194</v>
+        <v>451347</v>
       </c>
       <c r="R18" t="n">
-        <v>6709513</v>
+        <v>6709539</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863173</v>
+        <v>124863263</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451230</v>
+        <v>451367</v>
       </c>
       <c r="R19" t="n">
-        <v>6709603</v>
+        <v>6709547</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863180</v>
+        <v>124863173</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451234</v>
+        <v>451230</v>
       </c>
       <c r="R2" t="n">
-        <v>6709587</v>
+        <v>6709603</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863193</v>
+        <v>124862972</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451220</v>
+        <v>451167</v>
       </c>
       <c r="R3" t="n">
-        <v>6709614</v>
+        <v>6709559</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863010</v>
+        <v>124862912</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451163</v>
+        <v>451208</v>
       </c>
       <c r="R4" t="n">
-        <v>6709539</v>
+        <v>6709512</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124862955</v>
+        <v>124863208</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451085</v>
+        <v>451244</v>
       </c>
       <c r="R5" t="n">
-        <v>6709545</v>
+        <v>6709610</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863049</v>
+        <v>124863180</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451155</v>
+        <v>451234</v>
       </c>
       <c r="R6" t="n">
-        <v>6709561</v>
+        <v>6709587</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863201</v>
+        <v>124863258</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451250</v>
+        <v>451347</v>
       </c>
       <c r="R7" t="n">
-        <v>6709591</v>
+        <v>6709539</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863021</v>
+        <v>124863186</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451148</v>
+        <v>451213</v>
       </c>
       <c r="R8" t="n">
-        <v>6709550</v>
+        <v>6709596</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124862912</v>
+        <v>124863021</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451208</v>
+        <v>451148</v>
       </c>
       <c r="R9" t="n">
-        <v>6709512</v>
+        <v>6709550</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124862987</v>
+        <v>124863263</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451183</v>
+        <v>451367</v>
       </c>
       <c r="R10" t="n">
         <v>6709547</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863173</v>
+        <v>124863193</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451230</v>
+        <v>451220</v>
       </c>
       <c r="R11" t="n">
-        <v>6709603</v>
+        <v>6709614</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124862972</v>
+        <v>124862987</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451167</v>
+        <v>451183</v>
       </c>
       <c r="R12" t="n">
-        <v>6709559</v>
+        <v>6709547</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124862901</v>
+        <v>124862955</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451194</v>
+        <v>451085</v>
       </c>
       <c r="R13" t="n">
-        <v>6709513</v>
+        <v>6709545</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863186</v>
+        <v>124863157</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451213</v>
+        <v>451181</v>
       </c>
       <c r="R15" t="n">
-        <v>6709596</v>
+        <v>6709688</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863157</v>
+        <v>124863201</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451181</v>
+        <v>451250</v>
       </c>
       <c r="R16" t="n">
-        <v>6709688</v>
+        <v>6709591</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863208</v>
+        <v>124863010</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451244</v>
+        <v>451163</v>
       </c>
       <c r="R17" t="n">
-        <v>6709610</v>
+        <v>6709539</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863258</v>
+        <v>124863049</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451347</v>
+        <v>451155</v>
       </c>
       <c r="R18" t="n">
-        <v>6709539</v>
+        <v>6709561</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863263</v>
+        <v>124862901</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451367</v>
+        <v>451194</v>
       </c>
       <c r="R19" t="n">
-        <v>6709547</v>
+        <v>6709513</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863173</v>
+        <v>124862955</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451230</v>
+        <v>451085</v>
       </c>
       <c r="R2" t="n">
-        <v>6709603</v>
+        <v>6709545</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124862972</v>
+        <v>124863258</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451167</v>
+        <v>451347</v>
       </c>
       <c r="R3" t="n">
-        <v>6709559</v>
+        <v>6709539</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124862912</v>
+        <v>124863141</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451208</v>
+        <v>451172</v>
       </c>
       <c r="R4" t="n">
-        <v>6709512</v>
+        <v>6709678</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863208</v>
+        <v>124862987</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451244</v>
+        <v>451183</v>
       </c>
       <c r="R5" t="n">
-        <v>6709610</v>
+        <v>6709547</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863180</v>
+        <v>124863049</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451234</v>
+        <v>451155</v>
       </c>
       <c r="R6" t="n">
-        <v>6709587</v>
+        <v>6709561</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863258</v>
+        <v>124862901</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451347</v>
+        <v>451194</v>
       </c>
       <c r="R7" t="n">
-        <v>6709539</v>
+        <v>6709513</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863186</v>
+        <v>124863263</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451213</v>
+        <v>451367</v>
       </c>
       <c r="R8" t="n">
-        <v>6709596</v>
+        <v>6709547</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863021</v>
+        <v>124863157</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451148</v>
+        <v>451181</v>
       </c>
       <c r="R9" t="n">
-        <v>6709550</v>
+        <v>6709688</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863263</v>
+        <v>124862912</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451367</v>
+        <v>451208</v>
       </c>
       <c r="R10" t="n">
-        <v>6709547</v>
+        <v>6709512</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863193</v>
+        <v>124862972</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451220</v>
+        <v>451167</v>
       </c>
       <c r="R11" t="n">
-        <v>6709614</v>
+        <v>6709559</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124862987</v>
+        <v>124863208</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451183</v>
+        <v>451244</v>
       </c>
       <c r="R12" t="n">
-        <v>6709547</v>
+        <v>6709610</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124862955</v>
+        <v>124863201</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451085</v>
+        <v>451250</v>
       </c>
       <c r="R13" t="n">
-        <v>6709545</v>
+        <v>6709591</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863141</v>
+        <v>124863186</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451172</v>
+        <v>451213</v>
       </c>
       <c r="R14" t="n">
-        <v>6709678</v>
+        <v>6709596</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863157</v>
+        <v>124863173</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451181</v>
+        <v>451230</v>
       </c>
       <c r="R15" t="n">
-        <v>6709688</v>
+        <v>6709603</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863201</v>
+        <v>124863010</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451250</v>
+        <v>451163</v>
       </c>
       <c r="R16" t="n">
-        <v>6709591</v>
+        <v>6709539</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863010</v>
+        <v>124863021</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451163</v>
+        <v>451148</v>
       </c>
       <c r="R17" t="n">
-        <v>6709539</v>
+        <v>6709550</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863049</v>
+        <v>124863193</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451155</v>
+        <v>451220</v>
       </c>
       <c r="R18" t="n">
-        <v>6709561</v>
+        <v>6709614</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124862901</v>
+        <v>124863180</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451194</v>
+        <v>451234</v>
       </c>
       <c r="R19" t="n">
-        <v>6709513</v>
+        <v>6709587</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124862955</v>
+        <v>124863180</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451085</v>
+        <v>451234</v>
       </c>
       <c r="R2" t="n">
-        <v>6709545</v>
+        <v>6709587</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863258</v>
+        <v>124863021</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451347</v>
+        <v>451148</v>
       </c>
       <c r="R3" t="n">
-        <v>6709539</v>
+        <v>6709550</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863141</v>
+        <v>124862987</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451172</v>
+        <v>451183</v>
       </c>
       <c r="R4" t="n">
-        <v>6709678</v>
+        <v>6709547</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124862987</v>
+        <v>124863258</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451183</v>
+        <v>451347</v>
       </c>
       <c r="R5" t="n">
-        <v>6709547</v>
+        <v>6709539</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863049</v>
+        <v>124862955</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451155</v>
+        <v>451085</v>
       </c>
       <c r="R6" t="n">
-        <v>6709561</v>
+        <v>6709545</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124862901</v>
+        <v>124863141</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451194</v>
+        <v>451172</v>
       </c>
       <c r="R7" t="n">
-        <v>6709513</v>
+        <v>6709678</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863263</v>
+        <v>124863049</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451367</v>
+        <v>451155</v>
       </c>
       <c r="R8" t="n">
-        <v>6709547</v>
+        <v>6709561</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863157</v>
+        <v>124863186</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451181</v>
+        <v>451213</v>
       </c>
       <c r="R9" t="n">
-        <v>6709688</v>
+        <v>6709596</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124862972</v>
+        <v>124863263</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451167</v>
+        <v>451367</v>
       </c>
       <c r="R11" t="n">
-        <v>6709559</v>
+        <v>6709547</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863201</v>
+        <v>124863193</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451250</v>
+        <v>451220</v>
       </c>
       <c r="R13" t="n">
-        <v>6709591</v>
+        <v>6709614</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863186</v>
+        <v>124863157</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451213</v>
+        <v>451181</v>
       </c>
       <c r="R14" t="n">
-        <v>6709596</v>
+        <v>6709688</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863173</v>
+        <v>124863010</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451230</v>
+        <v>451163</v>
       </c>
       <c r="R15" t="n">
-        <v>6709603</v>
+        <v>6709539</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863010</v>
+        <v>124862972</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451163</v>
+        <v>451167</v>
       </c>
       <c r="R16" t="n">
-        <v>6709539</v>
+        <v>6709559</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863021</v>
+        <v>124863173</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451148</v>
+        <v>451230</v>
       </c>
       <c r="R17" t="n">
-        <v>6709550</v>
+        <v>6709603</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863193</v>
+        <v>124862901</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451220</v>
+        <v>451194</v>
       </c>
       <c r="R18" t="n">
-        <v>6709614</v>
+        <v>6709513</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863180</v>
+        <v>124863201</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451234</v>
+        <v>451250</v>
       </c>
       <c r="R19" t="n">
-        <v>6709587</v>
+        <v>6709591</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863180</v>
+        <v>124863263</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451234</v>
+        <v>451367</v>
       </c>
       <c r="R2" t="n">
-        <v>6709587</v>
+        <v>6709547</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863021</v>
+        <v>124862972</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451148</v>
+        <v>451167</v>
       </c>
       <c r="R3" t="n">
-        <v>6709550</v>
+        <v>6709559</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124862987</v>
+        <v>124863201</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451183</v>
+        <v>451250</v>
       </c>
       <c r="R4" t="n">
-        <v>6709547</v>
+        <v>6709591</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863258</v>
+        <v>124862955</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451347</v>
+        <v>451085</v>
       </c>
       <c r="R5" t="n">
-        <v>6709539</v>
+        <v>6709545</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124862955</v>
+        <v>124862912</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451085</v>
+        <v>451208</v>
       </c>
       <c r="R6" t="n">
-        <v>6709545</v>
+        <v>6709512</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863141</v>
+        <v>124863010</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451172</v>
+        <v>451163</v>
       </c>
       <c r="R7" t="n">
-        <v>6709678</v>
+        <v>6709539</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124862912</v>
+        <v>124862987</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451208</v>
+        <v>451183</v>
       </c>
       <c r="R10" t="n">
-        <v>6709512</v>
+        <v>6709547</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863263</v>
+        <v>124863180</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451367</v>
+        <v>451234</v>
       </c>
       <c r="R11" t="n">
-        <v>6709547</v>
+        <v>6709587</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863208</v>
+        <v>124863258</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451244</v>
+        <v>451347</v>
       </c>
       <c r="R12" t="n">
-        <v>6709610</v>
+        <v>6709539</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863157</v>
+        <v>124863141</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451181</v>
+        <v>451172</v>
       </c>
       <c r="R14" t="n">
-        <v>6709688</v>
+        <v>6709678</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863010</v>
+        <v>124863208</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451163</v>
+        <v>451244</v>
       </c>
       <c r="R15" t="n">
-        <v>6709539</v>
+        <v>6709610</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124862972</v>
+        <v>124863157</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451167</v>
+        <v>451181</v>
       </c>
       <c r="R16" t="n">
-        <v>6709559</v>
+        <v>6709688</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863173</v>
+        <v>124862901</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451230</v>
+        <v>451194</v>
       </c>
       <c r="R17" t="n">
-        <v>6709603</v>
+        <v>6709513</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124862901</v>
+        <v>124863173</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451194</v>
+        <v>451230</v>
       </c>
       <c r="R18" t="n">
-        <v>6709513</v>
+        <v>6709603</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863201</v>
+        <v>124863021</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451250</v>
+        <v>451148</v>
       </c>
       <c r="R19" t="n">
-        <v>6709591</v>
+        <v>6709550</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863263</v>
+        <v>124863258</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451367</v>
+        <v>451347</v>
       </c>
       <c r="R2" t="n">
-        <v>6709547</v>
+        <v>6709539</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124862972</v>
+        <v>124863193</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451167</v>
+        <v>451220</v>
       </c>
       <c r="R3" t="n">
-        <v>6709559</v>
+        <v>6709614</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863201</v>
+        <v>124863173</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451250</v>
+        <v>451230</v>
       </c>
       <c r="R4" t="n">
-        <v>6709591</v>
+        <v>6709603</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124862955</v>
+        <v>124863021</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451085</v>
+        <v>451148</v>
       </c>
       <c r="R5" t="n">
-        <v>6709545</v>
+        <v>6709550</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124862912</v>
+        <v>124863141</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451208</v>
+        <v>451172</v>
       </c>
       <c r="R6" t="n">
-        <v>6709512</v>
+        <v>6709678</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863010</v>
+        <v>124862987</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451163</v>
+        <v>451183</v>
       </c>
       <c r="R7" t="n">
-        <v>6709539</v>
+        <v>6709547</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863049</v>
+        <v>124862912</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451155</v>
+        <v>451208</v>
       </c>
       <c r="R8" t="n">
-        <v>6709561</v>
+        <v>6709512</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863186</v>
+        <v>124862972</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451213</v>
+        <v>451167</v>
       </c>
       <c r="R9" t="n">
-        <v>6709596</v>
+        <v>6709559</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124862987</v>
+        <v>124863208</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451183</v>
+        <v>451244</v>
       </c>
       <c r="R10" t="n">
-        <v>6709547</v>
+        <v>6709610</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863180</v>
+        <v>124863010</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451234</v>
+        <v>451163</v>
       </c>
       <c r="R11" t="n">
-        <v>6709587</v>
+        <v>6709539</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863258</v>
+        <v>124863201</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451347</v>
+        <v>451250</v>
       </c>
       <c r="R12" t="n">
-        <v>6709539</v>
+        <v>6709591</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863193</v>
+        <v>124863263</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451220</v>
+        <v>451367</v>
       </c>
       <c r="R13" t="n">
-        <v>6709614</v>
+        <v>6709547</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863141</v>
+        <v>124862901</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451172</v>
+        <v>451194</v>
       </c>
       <c r="R14" t="n">
-        <v>6709678</v>
+        <v>6709513</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863208</v>
+        <v>124863157</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451244</v>
+        <v>451181</v>
       </c>
       <c r="R15" t="n">
-        <v>6709610</v>
+        <v>6709688</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863157</v>
+        <v>124863049</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451181</v>
+        <v>451155</v>
       </c>
       <c r="R16" t="n">
-        <v>6709688</v>
+        <v>6709561</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124862901</v>
+        <v>124863186</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451194</v>
+        <v>451213</v>
       </c>
       <c r="R17" t="n">
-        <v>6709513</v>
+        <v>6709596</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863173</v>
+        <v>124863180</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451230</v>
+        <v>451234</v>
       </c>
       <c r="R18" t="n">
-        <v>6709603</v>
+        <v>6709587</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863021</v>
+        <v>124862955</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451148</v>
+        <v>451085</v>
       </c>
       <c r="R19" t="n">
-        <v>6709550</v>
+        <v>6709545</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863258</v>
+        <v>124863208</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451347</v>
+        <v>451244</v>
       </c>
       <c r="R2" t="n">
-        <v>6709539</v>
+        <v>6709610</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863193</v>
+        <v>124863258</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451220</v>
+        <v>451347</v>
       </c>
       <c r="R3" t="n">
-        <v>6709614</v>
+        <v>6709539</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863173</v>
+        <v>124863201</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451230</v>
+        <v>451250</v>
       </c>
       <c r="R4" t="n">
-        <v>6709603</v>
+        <v>6709591</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863021</v>
+        <v>124862955</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451148</v>
+        <v>451085</v>
       </c>
       <c r="R5" t="n">
-        <v>6709550</v>
+        <v>6709545</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124863141</v>
+        <v>124862901</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451172</v>
+        <v>451194</v>
       </c>
       <c r="R6" t="n">
-        <v>6709678</v>
+        <v>6709513</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124862987</v>
+        <v>124863010</v>
       </c>
       <c r="B7" t="n">
         <v>78947</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451183</v>
+        <v>451163</v>
       </c>
       <c r="R7" t="n">
-        <v>6709547</v>
+        <v>6709539</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124862912</v>
+        <v>124863180</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451208</v>
+        <v>451234</v>
       </c>
       <c r="R8" t="n">
-        <v>6709512</v>
+        <v>6709587</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124862972</v>
+        <v>124862912</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451167</v>
+        <v>451208</v>
       </c>
       <c r="R9" t="n">
-        <v>6709559</v>
+        <v>6709512</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863208</v>
+        <v>124863157</v>
       </c>
       <c r="B10" t="n">
         <v>78947</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451244</v>
+        <v>451181</v>
       </c>
       <c r="R10" t="n">
-        <v>6709610</v>
+        <v>6709688</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124863010</v>
+        <v>124862987</v>
       </c>
       <c r="B11" t="n">
         <v>78947</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451163</v>
+        <v>451183</v>
       </c>
       <c r="R11" t="n">
-        <v>6709539</v>
+        <v>6709547</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863201</v>
+        <v>124863141</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451250</v>
+        <v>451172</v>
       </c>
       <c r="R12" t="n">
-        <v>6709591</v>
+        <v>6709678</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863263</v>
+        <v>124863193</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451367</v>
+        <v>451220</v>
       </c>
       <c r="R13" t="n">
-        <v>6709547</v>
+        <v>6709614</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124862901</v>
+        <v>124863263</v>
       </c>
       <c r="B14" t="n">
         <v>78947</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451194</v>
+        <v>451367</v>
       </c>
       <c r="R14" t="n">
-        <v>6709513</v>
+        <v>6709547</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863157</v>
+        <v>124863173</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451181</v>
+        <v>451230</v>
       </c>
       <c r="R15" t="n">
-        <v>6709688</v>
+        <v>6709603</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863180</v>
+        <v>124863021</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451234</v>
+        <v>451148</v>
       </c>
       <c r="R18" t="n">
-        <v>6709587</v>
+        <v>6709550</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124862955</v>
+        <v>124862972</v>
       </c>
       <c r="B19" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451085</v>
+        <v>451167</v>
       </c>
       <c r="R19" t="n">
-        <v>6709545</v>
+        <v>6709559</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124863208</v>
+        <v>124862912</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451244</v>
+        <v>451208</v>
       </c>
       <c r="R2" t="n">
-        <v>6709610</v>
+        <v>6709512</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863258</v>
+        <v>124863021</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451347</v>
+        <v>451148</v>
       </c>
       <c r="R3" t="n">
-        <v>6709539</v>
+        <v>6709550</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124863201</v>
+        <v>124862901</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451250</v>
+        <v>451194</v>
       </c>
       <c r="R4" t="n">
-        <v>6709591</v>
+        <v>6709513</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124862955</v>
+        <v>124863049</v>
       </c>
       <c r="B5" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451085</v>
+        <v>451155</v>
       </c>
       <c r="R5" t="n">
-        <v>6709545</v>
+        <v>6709561</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124862901</v>
+        <v>124862987</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451194</v>
+        <v>451183</v>
       </c>
       <c r="R6" t="n">
-        <v>6709513</v>
+        <v>6709547</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,11 +1185,6 @@
       <c r="B7" t="n">
         <v>78947</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863180</v>
+        <v>124863208</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451234</v>
+        <v>451244</v>
       </c>
       <c r="R8" t="n">
-        <v>6709587</v>
+        <v>6709610</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124862912</v>
+        <v>124863201</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451208</v>
+        <v>451250</v>
       </c>
       <c r="R9" t="n">
-        <v>6709512</v>
+        <v>6709591</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1528,11 +1488,6 @@
       <c r="B10" t="n">
         <v>78947</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1629,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124862987</v>
+        <v>124862972</v>
       </c>
       <c r="B11" t="n">
         <v>78947</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451183</v>
+        <v>451167</v>
       </c>
       <c r="R11" t="n">
-        <v>6709547</v>
+        <v>6709559</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863141</v>
+        <v>124863193</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451172</v>
+        <v>451220</v>
       </c>
       <c r="R12" t="n">
-        <v>6709678</v>
+        <v>6709614</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1841,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124863193</v>
+        <v>124863141</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451220</v>
+        <v>451172</v>
       </c>
       <c r="R13" t="n">
-        <v>6709614</v>
+        <v>6709678</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1947,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863263</v>
+        <v>124863173</v>
       </c>
       <c r="B14" t="n">
         <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451367</v>
+        <v>451230</v>
       </c>
       <c r="R14" t="n">
-        <v>6709547</v>
+        <v>6709603</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2053,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124863173</v>
+        <v>124862955</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451230</v>
+        <v>451085</v>
       </c>
       <c r="R15" t="n">
-        <v>6709603</v>
+        <v>6709545</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2159,15 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124863049</v>
+        <v>124863180</v>
       </c>
       <c r="B16" t="n">
         <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451155</v>
+        <v>451234</v>
       </c>
       <c r="R16" t="n">
-        <v>6709561</v>
+        <v>6709587</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2265,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863186</v>
+        <v>124863263</v>
       </c>
       <c r="B17" t="n">
         <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451213</v>
+        <v>451367</v>
       </c>
       <c r="R17" t="n">
-        <v>6709596</v>
+        <v>6709547</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2371,15 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863021</v>
+        <v>124863258</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451148</v>
+        <v>451347</v>
       </c>
       <c r="R18" t="n">
-        <v>6709550</v>
+        <v>6709539</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2477,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124862972</v>
+        <v>124863186</v>
       </c>
       <c r="B19" t="n">
         <v>78947</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,10 +2430,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451167</v>
+        <v>451213</v>
       </c>
       <c r="R19" t="n">
-        <v>6709559</v>
+        <v>6709596</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,6 +2491,1925 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128678518</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>451065</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6709628</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Föfohål</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128676133</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56880</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>451051</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6709472</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sandbadade.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128676568</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>451227</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6709725</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128676160</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>451069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6709491</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128675896</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>451053</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6709479</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera meter längs stammen med ringhack, äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128676237</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>451256</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6709506</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128676484</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91478</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>451251</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6709574</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128676522</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90491</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>451203</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6709660</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128678551</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>451311</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6709668</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128676557</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>451186</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6709680</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128676602</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>451152</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6709741</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128676575</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>451285</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6709660</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128676614</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>451194</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6709719</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128676628</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>451214</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6709680</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128676593</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>451192</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6709700</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128678480</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>451104</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6709597</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128676541</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>451164</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6709723</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128676637</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>451224</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6709641</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128676133</v>
+        <v>128676568</v>
       </c>
       <c r="B21" t="n">
-        <v>56880</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,35 +2620,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2656,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451051</v>
+        <v>451227</v>
       </c>
       <c r="R21" t="n">
-        <v>6709472</v>
+        <v>6709725</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2686,17 +2681,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sandbadade.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,6 +2695,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2714,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128676568</v>
+        <v>128676133</v>
       </c>
       <c r="B22" t="n">
-        <v>92748</v>
+        <v>56880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,30 +2725,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2765,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451227</v>
+        <v>451051</v>
       </c>
       <c r="R22" t="n">
-        <v>6709725</v>
+        <v>6709472</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2795,12 +2791,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sandbadade.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,7 +2810,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128676237</v>
+        <v>128676522</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>90497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3054,31 +3054,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3086,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451256</v>
+        <v>451203</v>
       </c>
       <c r="R25" t="n">
-        <v>6709506</v>
+        <v>6709660</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3116,12 +3115,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3130,6 +3129,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128676522</v>
+        <v>128676237</v>
       </c>
       <c r="B27" t="n">
-        <v>90491</v>
+        <v>57686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3264,30 +3264,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3295,10 +3296,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451203</v>
+        <v>451256</v>
       </c>
       <c r="R27" t="n">
-        <v>6709660</v>
+        <v>6709506</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3325,12 +3326,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3339,7 +3340,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128676593</v>
+        <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>97460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3994,32 +3994,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4027,13 +4030,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451192</v>
+        <v>451104</v>
       </c>
       <c r="R34" t="n">
-        <v>6709700</v>
+        <v>6709597</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4057,12 +4060,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4090,10 +4103,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128678480</v>
+        <v>128676593</v>
       </c>
       <c r="B35" t="n">
-        <v>97454</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4101,35 +4114,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4137,13 +4147,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451104</v>
+        <v>451192</v>
       </c>
       <c r="R35" t="n">
-        <v>6709597</v>
+        <v>6709700</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4167,22 +4177,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128676568</v>
+        <v>128676133</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>56880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,30 +2620,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2651,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451227</v>
+        <v>451051</v>
       </c>
       <c r="R21" t="n">
-        <v>6709725</v>
+        <v>6709472</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2681,12 +2686,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sandbadade.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,7 +2705,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2714,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128676133</v>
+        <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>56880</v>
+        <v>92754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,35 +2734,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2761,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451051</v>
+        <v>451227</v>
       </c>
       <c r="R22" t="n">
-        <v>6709472</v>
+        <v>6709725</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2791,17 +2795,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Sandbadade.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,6 +2809,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128676160</v>
+        <v>128675896</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2861,7 +2861,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451069</v>
+        <v>451053</v>
       </c>
       <c r="R23" t="n">
-        <v>6709491</v>
+        <v>6709479</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2907,6 +2907,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera meter längs stammen med ringhack, äldre tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,10 +2938,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128675896</v>
+        <v>128676160</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2944,16 +2949,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2966,7 +2971,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451053</v>
+        <v>451069</v>
       </c>
       <c r="R24" t="n">
-        <v>6709479</v>
+        <v>6709491</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3012,11 +3017,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flera meter längs stammen med ringhack, äldre tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128676237</v>
+        <v>128678551</v>
       </c>
       <c r="B27" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3284,11 +3284,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3296,13 +3292,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451256</v>
+        <v>451311</v>
       </c>
       <c r="R27" t="n">
-        <v>6709506</v>
+        <v>6709668</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3329,9 +3325,24 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3358,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128678551</v>
+        <v>128676237</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,16 +3380,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3389,7 +3400,11 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3397,13 +3412,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451311</v>
+        <v>451256</v>
       </c>
       <c r="R28" t="n">
-        <v>6709668</v>
+        <v>6709506</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3430,24 +3445,9 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2726,7 +2726,7 @@
         <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128676522</v>
       </c>
       <c r="B25" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>128676557</v>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128676602</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>128676614</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>128676628</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>128676541</v>
       </c>
       <c r="B36" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>128676637</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2726,7 +2726,7 @@
         <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2496,7 +2496,7 @@
         <v>128678518</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>128676133</v>
       </c>
       <c r="B21" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>128675896</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128676160</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128676522</v>
       </c>
       <c r="B25" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>128678551</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128676237</v>
       </c>
       <c r="B28" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>128676557</v>
       </c>
       <c r="B29" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128676602</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>128676614</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>128676628</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>128676541</v>
       </c>
       <c r="B36" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>128676637</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2726,7 +2726,7 @@
         <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128676522</v>
       </c>
       <c r="B25" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>128676557</v>
       </c>
       <c r="B29" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128676602</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>128676614</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>128676628</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>128676541</v>
       </c>
       <c r="B36" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>128676637</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2726,7 +2726,7 @@
         <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128676522</v>
       </c>
       <c r="B25" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 2236-2025 artfynd.xlsx
+++ b/artfynd/A 2236-2025 artfynd.xlsx
@@ -2496,7 +2496,7 @@
         <v>128678518</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>128676133</v>
       </c>
       <c r="B21" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>128676568</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>128675896</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128676160</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128676522</v>
       </c>
       <c r="B25" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>128676484</v>
       </c>
       <c r="B26" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>128678551</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128676237</v>
       </c>
       <c r="B28" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>128676557</v>
       </c>
       <c r="B29" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128676602</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>128676575</v>
       </c>
       <c r="B31" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>128676614</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>128676628</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>128678480</v>
       </c>
       <c r="B34" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>128676541</v>
       </c>
       <c r="B36" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>128676637</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
